--- a/result_table_templates/DG_OSI_by_cell.xlsx
+++ b/result_table_templates/DG_OSI_by_cell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augustshin/Documents/GitHub/DJ_schwartzlab/result_table_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFE13CB-5F01-8C4C-9EA1-6FF075FE4E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8148F114-E343-5741-AA97-D7051BD4C8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43480" yWindow="6460" windowWidth="11800" windowHeight="20260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32300" yWindow="6400" windowWidth="11800" windowHeight="20260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,19 +94,19 @@
     <t>preferred angle for each condition</t>
   </si>
   <si>
-    <t>DSI_by_condition</t>
-  </si>
-  <si>
     <t>direction selectivity index for each condition</t>
   </si>
   <si>
-    <t>OSI_by_condition</t>
-  </si>
-  <si>
     <t>orientation selectivity index for each condition</t>
   </si>
   <si>
     <t>double</t>
+  </si>
+  <si>
+    <t>dsi_by_condition</t>
+  </si>
+  <si>
+    <t>osi_by_condition</t>
   </si>
 </sst>
 </file>
@@ -518,7 +518,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>20</v>
@@ -581,24 +581,24 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/result_table_templates/DG_OSI_by_cell.xlsx
+++ b/result_table_templates/DG_OSI_by_cell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augustshin/Documents/GitHub/DJ_schwartzlab/result_table_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8148F114-E343-5741-AA97-D7051BD4C8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76C1886-ACD0-5443-A3C7-B1E824A8E658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32300" yWindow="6400" windowWidth="11800" windowHeight="20260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Field</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>osi_by_condition</t>
+  </si>
+  <si>
+    <t>preferred_orientation_by_condition</t>
+  </si>
+  <si>
+    <t>preferred orientation for each condition</t>
   </si>
 </sst>
 </file>
@@ -461,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -581,23 +587,34 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
